--- a/data/trans_orig/IP31KM02_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM02_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4473</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1968</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8476</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,42%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14,06%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7970</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3719</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17426</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,16%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,21%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,41%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6093</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2549</t>
+          <t>2661</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>9159</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>14063</t>
+          <t>9757</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7836</t>
+          <t>5827</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23365</t>
+          <t>14803</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>55790</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>51787</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>58295</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>92,58%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>85,94%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,73%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>63430</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>53974</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>67681</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>88,84%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>75,59%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>94,79%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>68514</t>
+          <t>49638</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62805</t>
+          <t>45763</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72058</t>
+          <t>52261</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>131944</t>
+          <t>105429</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>122642</t>
+          <t>100383</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>138171</t>
+          <t>109359</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>53290</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>42405</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>64345</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>46,36%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>36,89%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>55,98%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>49722</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>21892</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>66753</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>39,57%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>17,42%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>53,13%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>58723</t>
+          <t>47230</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47297</t>
+          <t>38181</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70280</t>
+          <t>55805</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>108445</t>
+          <t>100520</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>75176</t>
+          <t>85623</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>127877</t>
+          <t>114203</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>53,3%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>61661</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>50606</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>72546</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>53,64%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>44,02%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>63,11%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>75927</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>58896</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>103757</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>60,43%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>46,87%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>82,58%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>67700</t>
+          <t>52103</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>56143</t>
+          <t>43528</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79126</t>
+          <t>61152</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>143626</t>
+          <t>113764</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>124194</t>
+          <t>100081</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>176895</t>
+          <t>128661</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>60,04%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>26701</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>21078</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>32970</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>46,6%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>36,79%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>57,54%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>23730</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>18425</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>29926</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>42,72%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>33,17%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>53,87%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>29661</t>
+          <t>22943</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23066</t>
+          <t>17539</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36121</t>
+          <t>28608</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>53391</t>
+          <t>49644</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44408</t>
+          <t>41494</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62614</t>
+          <t>57926</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>51,99%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>30598</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>24329</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>36221</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>53,4%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>42,46%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>63,21%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>31822</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>25626</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>37127</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>57,28%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>46,13%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>66,83%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>34972</t>
+          <t>31169</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28512</t>
+          <t>25504</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41567</t>
+          <t>36573</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>66794</t>
+          <t>61767</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>57571</t>
+          <t>53485</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>75777</t>
+          <t>69917</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>62,76%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>39543</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>24757</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>49435</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>56,64%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>35,46%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>70,81%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>47552</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>39814</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>54041</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>68,24%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>57,14%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>77,55%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>42171</t>
+          <t>48638</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25112</t>
+          <t>41827</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52883</t>
+          <t>55204</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>89723</t>
+          <t>88181</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65951</t>
+          <t>69851</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>102032</t>
+          <t>99857</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>71,19%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>30273</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20381</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>45059</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>43,36%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>29,19%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>64,54%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>22130</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>15641</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>29868</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>31,76%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>22,45%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>42,86%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>33196</t>
+          <t>21824</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22484</t>
+          <t>15258</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50255</t>
+          <t>28635</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>55326</t>
+          <t>52097</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43017</t>
+          <t>40421</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>79098</t>
+          <t>70427</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>50,21%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,74 +2092,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>33333</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>31085</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>97,46%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>90,89%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>34566</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>32054</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>35370</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>97,73%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>90,62%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>40719</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>136</t>
@@ -2167,27 +2167,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>74052</t>
+          <t>74145</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71625</t>
+          <t>71784</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2205,107 +2205,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>867</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>804</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3115</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3316</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>9,11%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>9,38%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>804</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>3165</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>867</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>3294</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>21965</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>16646</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>27186</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>46,53%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>35,26%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>57,59%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>16394</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>11763</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>21316</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>37,02%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>26,56%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>48,13%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25192</t>
+          <t>16337</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19165</t>
+          <t>11604</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31289</t>
+          <t>21382</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>41587</t>
+          <t>38303</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34221</t>
+          <t>31052</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49245</t>
+          <t>45585</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>49,82%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>25244</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>20023</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>30563</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>53,47%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>42,41%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>64,74%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>27896</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>22974</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>32527</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>62,98%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>51,87%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>73,44%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>28590</t>
+          <t>27949</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22493</t>
+          <t>22904</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34617</t>
+          <t>32682</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>56485</t>
+          <t>53192</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>48827</t>
+          <t>45910</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>63851</t>
+          <t>60443</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>66,06%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>87734</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>75139</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>98155</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>62,41%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>53,45%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>69,83%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>83172</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>72632</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>92633</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>67,24%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>58,72%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>74,89%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>96332</t>
+          <t>82059</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>80714</t>
+          <t>72584</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>109278</t>
+          <t>90297</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>179505</t>
+          <t>169793</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>159262</t>
+          <t>155649</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>193195</t>
+          <t>183743</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>70,03%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>52837</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>42416</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>65432</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>37,59%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>30,17%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>46,55%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>40524</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>31063</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>51064</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>32,76%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>25,11%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>41,28%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>58712</t>
+          <t>39763</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>45766</t>
+          <t>31525</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>74330</t>
+          <t>49238</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>99235</t>
+          <t>92601</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>85545</t>
+          <t>78651</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>119478</t>
+          <t>106745</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>40,68%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,72 +3121,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>137550</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>127405</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>144412</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>87,54%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>81,08%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>91,9%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>104447</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>94909</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>111323</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>81,18%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>73,76%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>86,52%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>134728</t>
+          <t>110761</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>126740</t>
+          <t>99821</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>141401</t>
+          <t>119383</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>239175</t>
+          <t>248311</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>226859</t>
+          <t>234193</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>249518</t>
+          <t>259777</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,05%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>19586</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>12724</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>29731</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>12,46%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>8,1%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>18,92%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>24218</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>17342</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>33756</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>18,82%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>13,48%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>26,24%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>19431</t>
+          <t>27139</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12758</t>
+          <t>18517</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>27419</t>
+          <t>38079</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>43648</t>
+          <t>46725</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>33305</t>
+          <t>35259</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>55964</t>
+          <t>60843</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>410834</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>384652</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>434676</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>59,82%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>56,0%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>63,29%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>544</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>366321</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>318794</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>395379</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>56,09%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>48,81%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>60,54%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>568</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>433620</t>
+          <t>367819</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>403613</t>
+          <t>346615</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>461505</t>
+          <t>386977</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>799941</t>
+          <t>778653</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>747858</t>
+          <t>744514</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>839350</t>
+          <t>813442</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>62,33%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>275990</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>252148</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>302172</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>40,18%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>36,71%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>44,0%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>371</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>286813</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>257755</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>334340</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>43,91%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>39,46%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>51,19%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>311113</t>
+          <t>250389</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>283228</t>
+          <t>231231</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>341120</t>
+          <t>271593</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>597926</t>
+          <t>526378</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>558517</t>
+          <t>491589</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>650009</t>
+          <t>560517</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>42,95%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
